--- a/output/2026-09-13_19_Croazia_Primorsko-goranska_Cleaning.xlsx
+++ b/output/2026-09-13_19_Croazia_Primorsko-goranska_Cleaning.xlsx
@@ -501,7 +501,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Centro Kärcher ufficiale (elencato su karcher.com), sede a Milutina Barača 54, Rijeka. Vendita e assistenza idropulitrici, aspirapolvere professionali, lavasciuga pavimenti. Opera anche filiali a Velika Gorica e Pula.</t>
+          <t>Centro Kärcher ufficiale (elencato su karcher.com), sede a Milutina Barača 54, Rijeka. Vendita e assistenza idropulitrici, aspirapolvere professionali, lavasciuga pavimenti. Opera anche filiali a Velika Gorica e Pula. [DUPLICATO — vedi anche: 2026-09-07_18_Croazia_Zagrebacka_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -536,10 +536,9 @@
           <t>+385 51 818 626</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Produttore/distributore di sistemi di ventilazione industriale e aspirazione polveri (otprašivanje): filtri, cicloni, ventilatori di trasporto. Sede confermata a Ravna Gora.</t>
+          <t>Produttore/distributore di sistemi di ventilazione industriale e aspirazione polveri (otprašivanje): filtri, cicloni, ventilatori di trasporto. Sede confermata a Ravna Gora. [DUPLICATO — vedi anche: 2026-09-12_23_Croazia_Varazdinska_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -581,7 +580,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Distributore e centro assistenza ufficiale Nilfisk e Viper per attrezzature professionali di pulizia industriale. Copertura dichiarata su tutta la Croazia; nessuna filiale fisica confermata a Rijeka.</t>
+          <t>Distributore e centro assistenza ufficiale Nilfisk e Viper per attrezzature professionali di pulizia industriale. Copertura dichiarata su tutta la Croazia; nessuna filiale fisica confermata a Rijeka. [DUPLICATO — vedi anche: 2026-09-07_19_Croazia_Zagrebacka_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">

--- a/output/2026-09-13_19_Croazia_Primorsko-goranska_Cleaning.xlsx
+++ b/output/2026-09-13_19_Croazia_Primorsko-goranska_Cleaning.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
